--- a/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-25).xlsx
+++ b/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-25).xlsx
@@ -912,33 +912,33 @@
   </si>
   <si>
     <t>214
-172</t>
-  </si>
-  <si>
-    <t>33</t>
-  </si>
-  <si>
-    <t>R$ 1.709.364,35</t>
-  </si>
-  <si>
-    <t>R$ 9.444,00
-R$ 9.558,45</t>
-  </si>
-  <si>
-    <t>(4.5%)
-(3.3%)</t>
-  </si>
-  <si>
-    <t>99.5</t>
-  </si>
-  <si>
-    <t>(6.2%)</t>
-  </si>
-  <si>
-    <t>249.9%</t>
-  </si>
-  <si>
-    <t>207.4%</t>
+174</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>R$ 1.730.699,26</t>
+  </si>
+  <si>
+    <t>R$ 9.405,97
+R$ 9.557,06</t>
+  </si>
+  <si>
+    <t>(5.2%)
+(3.6%)</t>
+  </si>
+  <si>
+    <t>99.1</t>
+  </si>
+  <si>
+    <t>(6.9%)</t>
+  </si>
+  <si>
+    <t>247.5%</t>
+  </si>
+  <si>
+    <t>205.2%</t>
   </si>
   <si>
     <t>2.7%</t>
@@ -950,10 +950,10 @@
     <t>29.6</t>
   </si>
   <si>
-    <t>59.4%</t>
-  </si>
-  <si>
-    <t>14.6%</t>
+    <t>59.5%</t>
+  </si>
+  <si>
+    <t>14.7%</t>
   </si>
   <si>
     <t>6.5</t>
@@ -968,13 +968,13 @@
     <t>21.2</t>
   </si>
   <si>
-    <t>63.2%</t>
-  </si>
-  <si>
-    <t>-R$ 49.445,98</t>
-  </si>
-  <si>
-    <t>2.95</t>
+    <t>63.0%</t>
+  </si>
+  <si>
+    <t>-R$ 52.127,80</t>
+  </si>
+  <si>
+    <t>2.94</t>
   </si>
   <si>
     <t>3.52</t>
@@ -1411,7 +1411,7 @@
     <col min="14" max="14" width="12.14" customWidth="1"/>
     <col min="15" max="15" width="15.29" customWidth="1"/>
     <col min="16" max="16" width="16" customWidth="1"/>
-    <col min="17" max="17" width="7.43" customWidth="1"/>
+    <col min="17" max="17" width="7.71" customWidth="1"/>
     <col min="18" max="18" width="10.14" customWidth="1"/>
     <col min="19" max="19" width="13.71" customWidth="1"/>
     <col min="20" max="20" width="12" customWidth="1"/>
@@ -1884,7 +1884,9 @@
       <c r="AB4" s="8">
         <v>4.7200720430107523</v>
       </c>
-      <c r="AC4" s="8"/>
+      <c r="AC4" s="8">
+        <v>18.83154</v>
+      </c>
       <c r="AD4" s="8">
         <v>24.065053763440861</v>
       </c>
@@ -2997,10 +2999,10 @@
         <v>0.042857142857142927</v>
       </c>
       <c r="T13" s="6">
-        <v>0.22893612355891904</v>
+        <v>0.21409572147056222</v>
       </c>
       <c r="U13" s="6">
-        <v>-0.11861317085685341</v>
+        <v>-0.13345357294521024</v>
       </c>
       <c r="V13" s="6">
         <v>0.022572979563017986</v>
@@ -4384,7 +4386,7 @@
         <v>19536</v>
       </c>
       <c r="B24" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C24" s="4">
         <v>44</v>
@@ -4420,25 +4422,59 @@
       <c t="s" r="N24" s="4">
         <v>52</v>
       </c>
-      <c r="O24" s="5"/>
-      <c r="P24" s="5"/>
-      <c r="Q24" s="6"/>
-      <c r="R24" s="7"/>
-      <c r="S24" s="6"/>
-      <c r="T24" s="6"/>
-      <c r="U24" s="6"/>
-      <c r="V24" s="6"/>
-      <c r="W24" s="6"/>
-      <c r="X24" s="8"/>
-      <c r="Y24" s="6"/>
-      <c r="Z24" s="6"/>
-      <c r="AA24" s="8"/>
-      <c r="AB24" s="8"/>
+      <c r="O24" s="5">
+        <v>10360.030000000001</v>
+      </c>
+      <c r="P24" s="5">
+        <v>10360.030000000001</v>
+      </c>
+      <c r="Q24" s="6">
+        <v>-0.099833869434582612</v>
+      </c>
+      <c r="R24" s="7">
+        <v>116</v>
+      </c>
+      <c r="S24" s="6">
+        <v>-0.16546762589928055</v>
+      </c>
+      <c r="T24" s="6">
+        <v>0.0054864705990233615</v>
+      </c>
+      <c r="U24" s="6">
+        <v>-0.33946233746427373</v>
+      </c>
+      <c r="V24" s="6">
+        <v>0.016012260582257</v>
+      </c>
+      <c r="W24" s="6">
+        <v>-0.0012772646411255565</v>
+      </c>
+      <c r="X24" s="8">
+        <v>29.949638043478263</v>
+      </c>
+      <c r="Y24" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="Z24" s="6">
+        <v>0.11956521739130435</v>
+      </c>
+      <c r="AA24" s="8">
+        <v>5.1401176991150441</v>
+      </c>
+      <c r="AB24" s="8">
+        <v>8.5481880434782607</v>
+      </c>
       <c r="AC24" s="8"/>
-      <c r="AD24" s="8"/>
-      <c r="AE24" s="6"/>
+      <c r="AD24" s="8">
+        <v>20.652355434782606</v>
+      </c>
+      <c r="AE24" s="6">
+        <v>0.54347826086956519</v>
+      </c>
       <c r="AF24" s="9"/>
-      <c r="AG24" s="5"/>
+      <c r="AG24" s="5">
+        <v>-151.90000000000001</v>
+      </c>
       <c r="AH24" s="10">
         <v>2</v>
       </c>
@@ -5706,10 +5742,10 @@
         <v>0.44508670520231219</v>
       </c>
       <c r="T34" s="6">
-        <v>0.032492126711404314</v>
+        <v>0.025357440198525268</v>
       </c>
       <c r="U34" s="6">
-        <v>-0.31645865398731748</v>
+        <v>-0.32359334050019656</v>
       </c>
       <c r="V34" s="6">
         <v>0.041501086869012153</v>
@@ -9333,7 +9369,7 @@
         <v>19632</v>
       </c>
       <c r="B63" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C63" s="4">
         <v>44</v>
@@ -9369,11 +9405,21 @@
       <c t="s" r="N63" s="4">
         <v>52</v>
       </c>
-      <c r="O63" s="5"/>
-      <c r="P63" s="5"/>
-      <c r="Q63" s="6"/>
-      <c r="R63" s="7"/>
-      <c r="S63" s="6"/>
+      <c r="O63" s="5">
+        <v>0</v>
+      </c>
+      <c r="P63" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="6">
+        <v>-1</v>
+      </c>
+      <c r="R63" s="7">
+        <v>101</v>
+      </c>
+      <c r="S63" s="6">
+        <v>-0.15833333333333333</v>
+      </c>
       <c r="T63" s="6"/>
       <c r="U63" s="6"/>
       <c r="V63" s="6"/>
@@ -9381,13 +9427,17 @@
       <c r="X63" s="8"/>
       <c r="Y63" s="6"/>
       <c r="Z63" s="6"/>
-      <c r="AA63" s="8"/>
+      <c r="AA63" s="8">
+        <v>0.19288058252427187</v>
+      </c>
       <c r="AB63" s="8"/>
       <c r="AC63" s="8"/>
       <c r="AD63" s="8"/>
       <c r="AE63" s="6"/>
       <c r="AF63" s="9"/>
-      <c r="AG63" s="5"/>
+      <c r="AG63" s="5">
+        <v>0</v>
+      </c>
       <c r="AH63" s="10">
         <v>3</v>
       </c>
@@ -12528,7 +12578,7 @@
         <v>-101.79000000000001</v>
       </c>
       <c r="AH88" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AI88" s="11"/>
       <c r="AJ88" s="13">
@@ -12567,7 +12617,7 @@
         <v>19693</v>
       </c>
       <c r="B89" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C89" s="4">
         <v>44</v>
@@ -12601,25 +12651,59 @@
       <c t="s" r="N89" s="4">
         <v>52</v>
       </c>
-      <c r="O89" s="5"/>
-      <c r="P89" s="5"/>
-      <c r="Q89" s="6"/>
-      <c r="R89" s="7"/>
-      <c r="S89" s="6"/>
-      <c r="T89" s="6"/>
-      <c r="U89" s="6"/>
-      <c r="V89" s="6"/>
-      <c r="W89" s="6"/>
-      <c r="X89" s="8"/>
-      <c r="Y89" s="6"/>
-      <c r="Z89" s="6"/>
-      <c r="AA89" s="8"/>
-      <c r="AB89" s="8"/>
+      <c r="O89" s="5">
+        <v>8514.7600000000002</v>
+      </c>
+      <c r="P89" s="5">
+        <v>8514.7600000000002</v>
+      </c>
+      <c r="Q89" s="6">
+        <v>-0.37505568876822681</v>
+      </c>
+      <c r="R89" s="7">
+        <v>77</v>
+      </c>
+      <c r="S89" s="6">
+        <v>-0.4031007751937985</v>
+      </c>
+      <c r="T89" s="6">
+        <v>1.5418251013534143</v>
+      </c>
+      <c r="U89" s="6">
+        <v>1.2038684237723671</v>
+      </c>
+      <c r="V89" s="6">
+        <v>0.023229368766706282</v>
+      </c>
+      <c r="W89" s="6">
+        <v>0.008330534272251949</v>
+      </c>
+      <c r="X89" s="8">
+        <v>43.087096774193547</v>
+      </c>
+      <c r="Y89" s="6">
+        <v>0.80645161290322576</v>
+      </c>
+      <c r="Z89" s="6">
+        <v>0.61290322580645162</v>
+      </c>
+      <c r="AA89" s="8">
+        <v>12.15458375</v>
+      </c>
+      <c r="AB89" s="8">
+        <v>9.4747322580645168</v>
+      </c>
       <c r="AC89" s="8"/>
-      <c r="AD89" s="8"/>
-      <c r="AE89" s="6"/>
+      <c r="AD89" s="8">
+        <v>32.428493548387095</v>
+      </c>
+      <c r="AE89" s="6">
+        <v>0.032258064516129031</v>
+      </c>
       <c r="AF89" s="9"/>
-      <c r="AG89" s="5"/>
+      <c r="AG89" s="5">
+        <v>-69.799999999999997</v>
+      </c>
       <c r="AH89" s="10">
         <v>2</v>
       </c>
@@ -16571,7 +16655,7 @@
         <v>0</v>
       </c>
       <c r="AH121" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI121" s="11"/>
       <c r="AJ121" s="13">
@@ -18534,7 +18618,7 @@
         <v>-274.39999999999998</v>
       </c>
       <c r="AH136" s="10">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AI136" s="11"/>
       <c r="AJ136" s="13">
@@ -20776,7 +20860,7 @@
         <v>100.5</v>
       </c>
       <c r="AH154" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AI154" s="11"/>
       <c r="AJ154" s="13">
@@ -27381,7 +27465,7 @@
         <v>19962</v>
       </c>
       <c r="B207" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C207" s="4">
         <v>44</v>
@@ -27417,25 +27501,57 @@
       <c t="s" r="N207" s="4">
         <v>52</v>
       </c>
-      <c r="O207" s="5"/>
-      <c r="P207" s="5"/>
+      <c r="O207" s="5">
+        <v>2460.1199999999999</v>
+      </c>
+      <c r="P207" s="5">
+        <v>2460.1199999999999</v>
+      </c>
       <c r="Q207" s="6"/>
-      <c r="R207" s="7"/>
+      <c r="R207" s="7">
+        <v>27</v>
+      </c>
       <c r="S207" s="6"/>
-      <c r="T207" s="6"/>
-      <c r="U207" s="6"/>
-      <c r="V207" s="6"/>
-      <c r="W207" s="6"/>
-      <c r="X207" s="8"/>
-      <c r="Y207" s="6"/>
-      <c r="Z207" s="6"/>
-      <c r="AA207" s="8"/>
-      <c r="AB207" s="8"/>
-      <c r="AC207" s="8"/>
-      <c r="AD207" s="8"/>
-      <c r="AE207" s="6"/>
+      <c r="T207" s="6">
+        <v>-0.014173698843958832</v>
+      </c>
+      <c r="U207" s="6">
+        <v>-0.36799383769897404</v>
+      </c>
+      <c r="V207" s="6">
+        <v>0.052978513243256427</v>
+      </c>
+      <c r="W207" s="6">
+        <v>-0.0052015755329008345</v>
+      </c>
+      <c r="X207" s="8">
+        <v>26.792594444444447</v>
+      </c>
+      <c r="Y207" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z207" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA207" s="8">
+        <v>7.8086407407407412</v>
+      </c>
+      <c r="AB207" s="8">
+        <v>6.9675944444444449</v>
+      </c>
+      <c r="AC207" s="8">
+        <v>14.753703</v>
+      </c>
+      <c r="AD207" s="8">
+        <v>21.717594444444444</v>
+      </c>
+      <c r="AE207" s="6">
+        <v>0.72222222222222221</v>
+      </c>
       <c r="AF207" s="9"/>
-      <c r="AG207" s="5"/>
+      <c r="AG207" s="5">
+        <v>-2460.1199999999999</v>
+      </c>
       <c r="AH207" s="10">
         <v>4</v>
       </c>

--- a/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-25).xlsx
+++ b/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-25).xlsx
@@ -912,33 +912,33 @@
   </si>
   <si>
     <t>214
-174</t>
-  </si>
-  <si>
-    <t>29</t>
-  </si>
-  <si>
-    <t>R$ 1.730.699,26</t>
-  </si>
-  <si>
-    <t>R$ 9.405,97
-R$ 9.557,06</t>
-  </si>
-  <si>
-    <t>(5.2%)
-(3.6%)</t>
-  </si>
-  <si>
-    <t>99.1</t>
-  </si>
-  <si>
-    <t>(6.9%)</t>
-  </si>
-  <si>
-    <t>247.5%</t>
-  </si>
-  <si>
-    <t>205.2%</t>
+181</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>R$ 1.788.460,04</t>
+  </si>
+  <si>
+    <t>R$ 9.363,67
+R$ 9.506,57</t>
+  </si>
+  <si>
+    <t>(5.5%)
+(4.0%)</t>
+  </si>
+  <si>
+    <t>98.6</t>
+  </si>
+  <si>
+    <t>(7.1%)</t>
+  </si>
+  <si>
+    <t>239.6%</t>
+  </si>
+  <si>
+    <t>197.6%</t>
   </si>
   <si>
     <t>2.7%</t>
@@ -947,31 +947,31 @@
     <t>0.6%</t>
   </si>
   <si>
-    <t>29.6</t>
-  </si>
-  <si>
-    <t>59.5%</t>
-  </si>
-  <si>
-    <t>14.7%</t>
-  </si>
-  <si>
-    <t>6.5</t>
+    <t>29.7</t>
+  </si>
+  <si>
+    <t>59.6%</t>
+  </si>
+  <si>
+    <t>15.1%</t>
+  </si>
+  <si>
+    <t>6.6</t>
   </si>
   <si>
     <t>7.6</t>
   </si>
   <si>
-    <t>14.5</t>
-  </si>
-  <si>
-    <t>21.2</t>
-  </si>
-  <si>
-    <t>63.0%</t>
-  </si>
-  <si>
-    <t>-R$ 52.127,80</t>
+    <t>14.6</t>
+  </si>
+  <si>
+    <t>21.3</t>
+  </si>
+  <si>
+    <t>62.7%</t>
+  </si>
+  <si>
+    <t>-R$ 52.308,70</t>
   </si>
   <si>
     <t>2.94</t>
@@ -2066,7 +2066,7 @@
         <v>19507</v>
       </c>
       <c r="B6" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C6" s="4">
         <v>44</v>
@@ -2102,25 +2102,61 @@
       <c t="s" r="N6" s="4">
         <v>52</v>
       </c>
-      <c r="O6" s="5"/>
-      <c r="P6" s="5"/>
-      <c r="Q6" s="6"/>
-      <c r="R6" s="7"/>
-      <c r="S6" s="6"/>
-      <c r="T6" s="6"/>
-      <c r="U6" s="6"/>
-      <c r="V6" s="6"/>
-      <c r="W6" s="6"/>
-      <c r="X6" s="8"/>
-      <c r="Y6" s="6"/>
-      <c r="Z6" s="6"/>
-      <c r="AA6" s="8"/>
-      <c r="AB6" s="8"/>
-      <c r="AC6" s="8"/>
-      <c r="AD6" s="8"/>
-      <c r="AE6" s="6"/>
+      <c r="O6" s="5">
+        <v>17094.07</v>
+      </c>
+      <c r="P6" s="5">
+        <v>17094.07</v>
+      </c>
+      <c r="Q6" s="6">
+        <v>-0.0048262295387371257</v>
+      </c>
+      <c r="R6" s="7">
+        <v>164</v>
+      </c>
+      <c r="S6" s="6">
+        <v>-0.035294117647058809</v>
+      </c>
+      <c r="T6" s="6">
+        <v>0.30236144464132886</v>
+      </c>
+      <c r="U6" s="6">
+        <v>-0.022359935346000104</v>
+      </c>
+      <c r="V6" s="6">
+        <v>0.026140217046028241</v>
+      </c>
+      <c r="W6" s="6">
+        <v>0.0046023387057617061</v>
+      </c>
+      <c r="X6" s="8">
+        <v>26.282070454545455</v>
+      </c>
+      <c r="Y6" s="6">
+        <v>0.96969696969696972</v>
+      </c>
+      <c r="Z6" s="6">
+        <v>0.045454545454545456</v>
+      </c>
+      <c r="AA6" s="8">
+        <v>11.305555757575757</v>
+      </c>
+      <c r="AB6" s="8">
+        <v>1.7263886363636363</v>
+      </c>
+      <c r="AC6" s="8">
+        <v>13.035226</v>
+      </c>
+      <c r="AD6" s="8">
+        <v>19.994949242424241</v>
+      </c>
+      <c r="AE6" s="6">
+        <v>0.74242424242424243</v>
+      </c>
       <c r="AF6" s="9"/>
-      <c r="AG6" s="5"/>
+      <c r="AG6" s="5">
+        <v>-80.900000000000006</v>
+      </c>
       <c r="AH6" s="10">
         <v>5</v>
       </c>
@@ -2999,10 +3035,10 @@
         <v>0.042857142857142927</v>
       </c>
       <c r="T13" s="6">
-        <v>0.21409572147056222</v>
+        <v>0.22893612355891904</v>
       </c>
       <c r="U13" s="6">
-        <v>-0.13345357294521024</v>
+        <v>-0.11861317085685341</v>
       </c>
       <c r="V13" s="6">
         <v>0.022572979563017986</v>
@@ -3025,7 +3061,9 @@
       <c r="AB13" s="8">
         <v>9.5576670000000004</v>
       </c>
-      <c r="AC13" s="8"/>
+      <c r="AC13" s="8">
+        <v>17.396939</v>
+      </c>
       <c r="AD13" s="8">
         <v>24.205775247524752</v>
       </c>
@@ -5875,10 +5913,10 @@
         <v>0.4375</v>
       </c>
       <c r="T35" s="6">
-        <v>2.0981942190675236</v>
+        <v>0.083209526706538611</v>
       </c>
       <c r="U35" s="6">
-        <v>-0.087404687248800322</v>
+        <v>-2.1023893796097854</v>
       </c>
       <c r="V35" s="6">
         <v>0.046737859428800106</v>
@@ -5956,7 +5994,7 @@
         <v>19562</v>
       </c>
       <c r="B36" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C36" s="4">
         <v>44</v>
@@ -5992,25 +6030,61 @@
       <c t="s" r="N36" s="4">
         <v>52</v>
       </c>
-      <c r="O36" s="5"/>
-      <c r="P36" s="5"/>
-      <c r="Q36" s="6"/>
-      <c r="R36" s="7"/>
-      <c r="S36" s="6"/>
-      <c r="T36" s="6"/>
-      <c r="U36" s="6"/>
-      <c r="V36" s="6"/>
-      <c r="W36" s="6"/>
-      <c r="X36" s="8"/>
-      <c r="Y36" s="6"/>
-      <c r="Z36" s="6"/>
-      <c r="AA36" s="8"/>
-      <c r="AB36" s="8"/>
-      <c r="AC36" s="8"/>
-      <c r="AD36" s="8"/>
-      <c r="AE36" s="6"/>
+      <c r="O36" s="5">
+        <v>9305.6399999999994</v>
+      </c>
+      <c r="P36" s="5">
+        <v>9305.6399999999994</v>
+      </c>
+      <c r="Q36" s="6">
+        <v>0.14323834235084232</v>
+      </c>
+      <c r="R36" s="7">
+        <v>122</v>
+      </c>
+      <c r="S36" s="6">
+        <v>0.60526315789473695</v>
+      </c>
+      <c r="T36" s="6">
+        <v>0.31746511792848209</v>
+      </c>
+      <c r="U36" s="6">
+        <v>-0.01528039984353575</v>
+      </c>
+      <c r="V36" s="6">
+        <v>0.041293237219578664</v>
+      </c>
+      <c r="W36" s="6">
+        <v>0.012855644533852588</v>
+      </c>
+      <c r="X36" s="8">
+        <v>32.861702127659576</v>
+      </c>
+      <c r="Y36" s="6">
+        <v>0.85106382978723405</v>
+      </c>
+      <c r="Z36" s="6">
+        <v>0.2978723404255319</v>
+      </c>
+      <c r="AA36" s="8">
+        <v>9.0290983606557376</v>
+      </c>
+      <c r="AB36" s="8">
+        <v>7.7044329787234034</v>
+      </c>
+      <c r="AC36" s="8">
+        <v>17.275659999999998</v>
+      </c>
+      <c r="AD36" s="8">
+        <v>24.291135106382978</v>
+      </c>
+      <c r="AE36" s="6">
+        <v>0.48936170212765956</v>
+      </c>
       <c r="AF36" s="9"/>
-      <c r="AG36" s="5"/>
+      <c r="AG36" s="5">
+        <v>0</v>
+      </c>
       <c r="AH36" s="10">
         <v>4</v>
       </c>
@@ -6706,7 +6780,7 @@
         <v>19579</v>
       </c>
       <c r="B42" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C42" s="4">
         <v>44</v>
@@ -6742,25 +6816,61 @@
       <c t="s" r="N42" s="4">
         <v>52</v>
       </c>
-      <c r="O42" s="5"/>
-      <c r="P42" s="5"/>
-      <c r="Q42" s="6"/>
-      <c r="R42" s="7"/>
-      <c r="S42" s="6"/>
-      <c r="T42" s="6"/>
-      <c r="U42" s="6"/>
-      <c r="V42" s="6"/>
-      <c r="W42" s="6"/>
-      <c r="X42" s="8"/>
-      <c r="Y42" s="6"/>
-      <c r="Z42" s="6"/>
-      <c r="AA42" s="8"/>
-      <c r="AB42" s="8"/>
-      <c r="AC42" s="8"/>
-      <c r="AD42" s="8"/>
-      <c r="AE42" s="6"/>
+      <c r="O42" s="5">
+        <v>8556.0400000000009</v>
+      </c>
+      <c r="P42" s="5">
+        <v>8556.0400000000009</v>
+      </c>
+      <c r="Q42" s="6">
+        <v>-0.2130126408563735</v>
+      </c>
+      <c r="R42" s="7">
+        <v>95</v>
+      </c>
+      <c r="S42" s="6">
+        <v>-0.16666666666666663</v>
+      </c>
+      <c r="T42" s="6">
+        <v>0.33358491778907062</v>
+      </c>
+      <c r="U42" s="6">
+        <v>0.017608134136820303</v>
+      </c>
+      <c r="V42" s="6">
+        <v>0.041884446543026914</v>
+      </c>
+      <c r="W42" s="6">
+        <v>0.012903749865592024</v>
+      </c>
+      <c r="X42" s="8">
+        <v>38.816926562500001</v>
+      </c>
+      <c r="Y42" s="6">
+        <v>0.3125</v>
+      </c>
+      <c r="Z42" s="6">
+        <v>0.359375</v>
+      </c>
+      <c r="AA42" s="8">
+        <v>7.2072691489361702</v>
+      </c>
+      <c r="AB42" s="8">
+        <v>15.76953125</v>
+      </c>
+      <c r="AC42" s="8">
+        <v>24.195171999999999</v>
+      </c>
+      <c r="AD42" s="8">
+        <v>28.975000000000001</v>
+      </c>
+      <c r="AE42" s="6">
+        <v>0.484375</v>
+      </c>
       <c r="AF42" s="9"/>
-      <c r="AG42" s="5"/>
+      <c r="AG42" s="5">
+        <v>-100</v>
+      </c>
       <c r="AH42" s="10">
         <v>3</v>
       </c>
@@ -7841,7 +7951,7 @@
         <v>19602</v>
       </c>
       <c r="B51" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C51" s="4">
         <v>44</v>
@@ -7877,25 +7987,61 @@
       <c t="s" r="N51" s="4">
         <v>52</v>
       </c>
-      <c r="O51" s="5"/>
-      <c r="P51" s="5"/>
-      <c r="Q51" s="6"/>
-      <c r="R51" s="7"/>
-      <c r="S51" s="6"/>
-      <c r="T51" s="6"/>
-      <c r="U51" s="6"/>
-      <c r="V51" s="6"/>
-      <c r="W51" s="6"/>
-      <c r="X51" s="8"/>
-      <c r="Y51" s="6"/>
-      <c r="Z51" s="6"/>
-      <c r="AA51" s="8"/>
-      <c r="AB51" s="8"/>
-      <c r="AC51" s="8"/>
-      <c r="AD51" s="8"/>
-      <c r="AE51" s="6"/>
+      <c r="O51" s="5">
+        <v>909.29999999999995</v>
+      </c>
+      <c r="P51" s="5">
+        <v>909.29999999999995</v>
+      </c>
+      <c r="Q51" s="6">
+        <v>-0.63473126054470952</v>
+      </c>
+      <c r="R51" s="7">
+        <v>9</v>
+      </c>
+      <c r="S51" s="6">
+        <v>-0.60869565217391308</v>
+      </c>
+      <c r="T51" s="6">
+        <v>0</v>
+      </c>
+      <c r="U51" s="6">
+        <v>-0.33410315627405701</v>
+      </c>
+      <c r="V51" s="6">
+        <v>0.042495875948531839</v>
+      </c>
+      <c r="W51" s="6">
+        <v>-0.11274441878367976</v>
+      </c>
+      <c r="X51" s="8">
+        <v>31.570824999999999</v>
+      </c>
+      <c r="Y51" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z51" s="6">
+        <v>0.25</v>
+      </c>
+      <c r="AA51" s="8">
+        <v>4.3037000000000001</v>
+      </c>
+      <c r="AB51" s="8">
+        <v>15.320824999999999</v>
+      </c>
+      <c r="AC51" s="8">
+        <v>20.445833</v>
+      </c>
+      <c r="AD51" s="8">
+        <v>27.358325000000001</v>
+      </c>
+      <c r="AE51" s="6">
+        <v>0.75</v>
+      </c>
       <c r="AF51" s="9"/>
-      <c r="AG51" s="5"/>
+      <c r="AG51" s="5">
+        <v>0</v>
+      </c>
       <c r="AH51" s="10">
         <v>2</v>
       </c>
@@ -14272,7 +14418,7 @@
         <v>19719</v>
       </c>
       <c r="B102" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C102" s="4">
         <v>44</v>
@@ -14308,25 +14454,61 @@
       <c t="s" r="N102" s="4">
         <v>52</v>
       </c>
-      <c r="O102" s="5"/>
-      <c r="P102" s="5"/>
-      <c r="Q102" s="6"/>
-      <c r="R102" s="7"/>
-      <c r="S102" s="6"/>
-      <c r="T102" s="6"/>
-      <c r="U102" s="6"/>
-      <c r="V102" s="6"/>
-      <c r="W102" s="6"/>
-      <c r="X102" s="8"/>
-      <c r="Y102" s="6"/>
-      <c r="Z102" s="6"/>
-      <c r="AA102" s="8"/>
-      <c r="AB102" s="8"/>
-      <c r="AC102" s="8"/>
-      <c r="AD102" s="8"/>
-      <c r="AE102" s="6"/>
+      <c r="O102" s="5">
+        <v>6985.2299999999996</v>
+      </c>
+      <c r="P102" s="5">
+        <v>6985.2299999999996</v>
+      </c>
+      <c r="Q102" s="6">
+        <v>0.0082344858245599895</v>
+      </c>
+      <c r="R102" s="7">
+        <v>68</v>
+      </c>
+      <c r="S102" s="6">
+        <v>-0.11688311688311692</v>
+      </c>
+      <c r="T102" s="6">
+        <v>0.27208113404998835</v>
+      </c>
+      <c r="U102" s="6">
+        <v>-0.056353291158630428</v>
+      </c>
+      <c r="V102" s="6">
+        <v>0.015370789508720544</v>
+      </c>
+      <c r="W102" s="6">
+        <v>0.00010572307568970529</v>
+      </c>
+      <c r="X102" s="8">
+        <v>45.001665999999993</v>
+      </c>
+      <c r="Y102" s="6">
+        <v>0.12</v>
+      </c>
+      <c r="Z102" s="6">
+        <v>0.59999999999999998</v>
+      </c>
+      <c r="AA102" s="8">
+        <v>13.962076811594203</v>
+      </c>
+      <c r="AB102" s="8">
+        <v>8.9788888888888891</v>
+      </c>
+      <c r="AC102" s="8">
+        <v>23.554051000000001</v>
+      </c>
+      <c r="AD102" s="8">
+        <v>29.206334000000002</v>
+      </c>
+      <c r="AE102" s="6">
+        <v>0.10000000000000001</v>
+      </c>
       <c r="AF102" s="9"/>
-      <c r="AG102" s="5"/>
+      <c r="AG102" s="5">
+        <v>0</v>
+      </c>
       <c r="AH102" s="10">
         <v>2</v>
       </c>
@@ -20413,7 +20595,7 @@
         <v>19821</v>
       </c>
       <c r="B151" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C151" s="4">
         <v>44</v>
@@ -20449,25 +20631,61 @@
       <c t="s" r="N151" s="4">
         <v>52</v>
       </c>
-      <c r="O151" s="5"/>
-      <c r="P151" s="5"/>
-      <c r="Q151" s="6"/>
-      <c r="R151" s="7"/>
-      <c r="S151" s="6"/>
-      <c r="T151" s="6"/>
-      <c r="U151" s="6"/>
-      <c r="V151" s="6"/>
-      <c r="W151" s="6"/>
-      <c r="X151" s="8"/>
-      <c r="Y151" s="6"/>
-      <c r="Z151" s="6"/>
-      <c r="AA151" s="8"/>
-      <c r="AB151" s="8"/>
-      <c r="AC151" s="8"/>
-      <c r="AD151" s="8"/>
-      <c r="AE151" s="6"/>
+      <c r="O151" s="5">
+        <v>6597.5900000000001</v>
+      </c>
+      <c r="P151" s="5">
+        <v>6597.5900000000001</v>
+      </c>
+      <c r="Q151" s="6">
+        <v>-0.39709825222561146</v>
+      </c>
+      <c r="R151" s="7">
+        <v>71</v>
+      </c>
+      <c r="S151" s="6">
+        <v>-0.37168141592920356</v>
+      </c>
+      <c r="T151" s="6">
+        <v>0.36140780193979927</v>
+      </c>
+      <c r="U151" s="6">
+        <v>0.047493175538340517</v>
+      </c>
+      <c r="V151" s="6">
+        <v>0.039023037199947257</v>
+      </c>
+      <c r="W151" s="6">
+        <v>0.014511056309955604</v>
+      </c>
+      <c r="X151" s="8">
+        <v>23.467543859649126</v>
+      </c>
+      <c r="Y151" s="6">
+        <v>0.61403508771929827</v>
+      </c>
+      <c r="Z151" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA151" s="8">
+        <v>4.8927225352112682</v>
+      </c>
+      <c r="AB151" s="8">
+        <v>2.5260228070175441</v>
+      </c>
+      <c r="AC151" s="8">
+        <v>7.3283620000000003</v>
+      </c>
+      <c r="AD151" s="8">
+        <v>14.274854385964913</v>
+      </c>
+      <c r="AE151" s="6">
+        <v>0.92982456140350878</v>
+      </c>
       <c r="AF151" s="9"/>
-      <c r="AG151" s="5"/>
+      <c r="AG151" s="5">
+        <v>0</v>
+      </c>
       <c r="AH151" s="10">
         <v>5</v>
       </c>
@@ -21254,7 +21472,7 @@
         <v>19859</v>
       </c>
       <c r="B158" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C158" s="4">
         <v>44</v>
@@ -21290,25 +21508,61 @@
       <c t="s" r="N158" s="4">
         <v>52</v>
       </c>
-      <c r="O158" s="5"/>
-      <c r="P158" s="5"/>
-      <c r="Q158" s="6"/>
-      <c r="R158" s="7"/>
-      <c r="S158" s="6"/>
-      <c r="T158" s="6"/>
-      <c r="U158" s="6"/>
-      <c r="V158" s="6"/>
-      <c r="W158" s="6"/>
-      <c r="X158" s="8"/>
-      <c r="Y158" s="6"/>
-      <c r="Z158" s="6"/>
-      <c r="AA158" s="8"/>
-      <c r="AB158" s="8"/>
-      <c r="AC158" s="8"/>
-      <c r="AD158" s="8"/>
-      <c r="AE158" s="6"/>
+      <c r="O158" s="5">
+        <v>8312.9099999999999</v>
+      </c>
+      <c r="P158" s="5">
+        <v>8312.9099999999999</v>
+      </c>
+      <c r="Q158" s="6">
+        <v>-0.18871211411439548</v>
+      </c>
+      <c r="R158" s="7">
+        <v>73</v>
+      </c>
+      <c r="S158" s="6">
+        <v>-0.32407407407407407</v>
+      </c>
+      <c r="T158" s="6">
+        <v>0.29383040355302775</v>
+      </c>
+      <c r="U158" s="6">
+        <v>-0.0028478956225918479</v>
+      </c>
+      <c r="V158" s="6">
+        <v>0.037879334673417614</v>
+      </c>
+      <c r="W158" s="6">
+        <v>0.009575166818839612</v>
+      </c>
+      <c r="X158" s="8">
+        <v>39.370161290322578</v>
+      </c>
+      <c r="Y158" s="6">
+        <v>0.32258064516129031</v>
+      </c>
+      <c r="Z158" s="6">
+        <v>0.45161290322580644</v>
+      </c>
+      <c r="AA158" s="8">
+        <v>9.8145833333333332</v>
+      </c>
+      <c r="AB158" s="8">
+        <v>6.7771499999999998</v>
+      </c>
+      <c r="AC158" s="8">
+        <v>16.840858999999998</v>
+      </c>
+      <c r="AD158" s="8">
+        <v>23.772580645161291</v>
+      </c>
+      <c r="AE158" s="6">
+        <v>0.20967741935483872</v>
+      </c>
       <c r="AF158" s="9"/>
-      <c r="AG158" s="5"/>
+      <c r="AG158" s="5">
+        <v>0</v>
+      </c>
       <c r="AH158" s="10">
         <v>2</v>
       </c>
@@ -26057,7 +26311,9 @@
       <c r="AB195" s="8">
         <v>10.086222666666666</v>
       </c>
-      <c r="AC195" s="8"/>
+      <c r="AC195" s="8">
+        <v>15.817999</v>
+      </c>
       <c r="AD195" s="8">
         <v>22.733556</v>
       </c>
